--- a/db/tablas_procesadas/Materia.xlsx
+++ b/db/tablas_procesadas/Materia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Posgrado\Proyecto Titulacion\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A11318-40C2-4C1F-8137-8C3354724911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F39AF44-B576-44E2-A9E5-9AAA5184F437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="4695" windowWidth="28785" windowHeight="15345" xr2:uid="{73FF22F9-0A89-43F3-8B4B-2BA89E274F19}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{73FF22F9-0A89-43F3-8B4B-2BA89E274F19}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="154">
   <si>
     <t>nombre_materia</t>
   </si>
@@ -499,43 +499,13 @@
   </si>
   <si>
     <t>tipo_materia</t>
-  </si>
-  <si>
-    <t>Todos</t>
-  </si>
-  <si>
-    <t>Guitarra</t>
-  </si>
-  <si>
-    <t>Piano</t>
-  </si>
-  <si>
-    <t>Direccion</t>
-  </si>
-  <si>
-    <t>Canto</t>
-  </si>
-  <si>
-    <t>Cuerda</t>
-  </si>
-  <si>
-    <t>Viento</t>
-  </si>
-  <si>
-    <t>Percusion</t>
-  </si>
-  <si>
-    <t>cantidad_docente</t>
-  </si>
-  <si>
-    <t>seccion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -900,17 +870,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA8CF66-513C-4C40-9688-A116B35459D8}">
-  <dimension ref="A1:F112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <dimension ref="A1:D112"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.25" customWidth="1"/>
-    <col min="2" max="2" width="23.125" customWidth="1"/>
-    <col min="3" max="3" width="21.875" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>151</v>
       </c>
@@ -923,14 +892,8 @@
       <c r="D1" t="s">
         <v>153</v>
       </c>
-      <c r="E1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -943,14 +906,8 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -963,14 +920,8 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -983,14 +934,8 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1003,14 +948,8 @@
       <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" t="s">
-        <v>154</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1023,14 +962,8 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1043,14 +976,8 @@
       <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1063,14 +990,8 @@
       <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1083,14 +1004,8 @@
       <c r="D9" t="s">
         <v>9</v>
       </c>
-      <c r="E9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1103,14 +1018,8 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
-      <c r="E10" t="s">
-        <v>154</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1123,14 +1032,8 @@
       <c r="D11" t="s">
         <v>9</v>
       </c>
-      <c r="E11" t="s">
-        <v>154</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1143,14 +1046,8 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
-      <c r="E12" t="s">
-        <v>154</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1163,14 +1060,8 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
-      <c r="E13" t="s">
-        <v>154</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1183,14 +1074,8 @@
       <c r="D14" t="s">
         <v>9</v>
       </c>
-      <c r="E14" t="s">
-        <v>154</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1203,14 +1088,8 @@
       <c r="D15" t="s">
         <v>9</v>
       </c>
-      <c r="E15" t="s">
-        <v>154</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1223,14 +1102,8 @@
       <c r="D16" t="s">
         <v>9</v>
       </c>
-      <c r="E16" t="s">
-        <v>154</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1243,14 +1116,8 @@
       <c r="D17" t="s">
         <v>9</v>
       </c>
-      <c r="E17" t="s">
-        <v>154</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -1263,14 +1130,8 @@
       <c r="D18" t="s">
         <v>9</v>
       </c>
-      <c r="E18" t="s">
-        <v>154</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1283,14 +1144,8 @@
       <c r="D19" t="s">
         <v>9</v>
       </c>
-      <c r="E19" t="s">
-        <v>154</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -1303,14 +1158,8 @@
       <c r="D20" t="s">
         <v>9</v>
       </c>
-      <c r="E20" t="s">
-        <v>154</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -1323,14 +1172,8 @@
       <c r="D21" t="s">
         <v>9</v>
       </c>
-      <c r="E21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -1343,14 +1186,8 @@
       <c r="D22" t="s">
         <v>9</v>
       </c>
-      <c r="E22" t="s">
-        <v>154</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -1363,14 +1200,8 @@
       <c r="D23" t="s">
         <v>9</v>
       </c>
-      <c r="E23" t="s">
-        <v>154</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -1383,14 +1214,8 @@
       <c r="D24" t="s">
         <v>9</v>
       </c>
-      <c r="E24" t="s">
-        <v>154</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1403,14 +1228,8 @@
       <c r="D25" t="s">
         <v>9</v>
       </c>
-      <c r="E25" t="s">
-        <v>154</v>
-      </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -1423,14 +1242,8 @@
       <c r="D26" t="s">
         <v>9</v>
       </c>
-      <c r="E26" t="s">
-        <v>154</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -1443,14 +1256,8 @@
       <c r="D27" t="s">
         <v>9</v>
       </c>
-      <c r="E27" t="s">
-        <v>154</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1463,14 +1270,8 @@
       <c r="D28" t="s">
         <v>9</v>
       </c>
-      <c r="E28" t="s">
-        <v>154</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -1483,14 +1284,8 @@
       <c r="D29" t="s">
         <v>9</v>
       </c>
-      <c r="E29" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -1503,14 +1298,8 @@
       <c r="D30" t="s">
         <v>9</v>
       </c>
-      <c r="E30" t="s">
-        <v>154</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -1523,14 +1312,8 @@
       <c r="D31" t="s">
         <v>9</v>
       </c>
-      <c r="E31" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -1543,14 +1326,8 @@
       <c r="D32" t="s">
         <v>9</v>
       </c>
-      <c r="E32" t="s">
-        <v>154</v>
-      </c>
-      <c r="F32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -1563,14 +1340,8 @@
       <c r="D33" t="s">
         <v>9</v>
       </c>
-      <c r="E33" t="s">
-        <v>154</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -1583,14 +1354,8 @@
       <c r="D34" t="s">
         <v>9</v>
       </c>
-      <c r="E34" t="s">
-        <v>154</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -1603,14 +1368,8 @@
       <c r="D35" t="s">
         <v>9</v>
       </c>
-      <c r="E35" t="s">
-        <v>154</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1623,14 +1382,8 @@
       <c r="D36" t="s">
         <v>9</v>
       </c>
-      <c r="E36" t="s">
-        <v>154</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -1643,14 +1396,8 @@
       <c r="D37" t="s">
         <v>9</v>
       </c>
-      <c r="E37" t="s">
-        <v>154</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -1663,14 +1410,8 @@
       <c r="D38" t="s">
         <v>9</v>
       </c>
-      <c r="E38" t="s">
-        <v>154</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -1683,14 +1424,8 @@
       <c r="D39" t="s">
         <v>9</v>
       </c>
-      <c r="E39" t="s">
-        <v>154</v>
-      </c>
-      <c r="F39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -1703,14 +1438,8 @@
       <c r="D40" t="s">
         <v>9</v>
       </c>
-      <c r="E40" t="s">
-        <v>154</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -1723,14 +1452,8 @@
       <c r="D41" t="s">
         <v>9</v>
       </c>
-      <c r="E41" t="s">
-        <v>154</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -1743,14 +1466,8 @@
       <c r="D42" t="s">
         <v>9</v>
       </c>
-      <c r="E42" t="s">
-        <v>154</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>58</v>
       </c>
@@ -1763,14 +1480,8 @@
       <c r="D43" t="s">
         <v>9</v>
       </c>
-      <c r="E43" t="s">
-        <v>154</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -1783,14 +1494,8 @@
       <c r="D44" t="s">
         <v>9</v>
       </c>
-      <c r="E44" t="s">
-        <v>154</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>60</v>
       </c>
@@ -1803,14 +1508,8 @@
       <c r="D45" t="s">
         <v>9</v>
       </c>
-      <c r="E45" t="s">
-        <v>154</v>
-      </c>
-      <c r="F45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -1823,14 +1522,8 @@
       <c r="D46" t="s">
         <v>9</v>
       </c>
-      <c r="E46" t="s">
-        <v>154</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -1843,14 +1536,8 @@
       <c r="D47" t="s">
         <v>9</v>
       </c>
-      <c r="E47" t="s">
-        <v>154</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>63</v>
       </c>
@@ -1863,14 +1550,8 @@
       <c r="D48" t="s">
         <v>9</v>
       </c>
-      <c r="E48" t="s">
-        <v>154</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>64</v>
       </c>
@@ -1883,14 +1564,8 @@
       <c r="D49" t="s">
         <v>9</v>
       </c>
-      <c r="E49" t="s">
-        <v>154</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>65</v>
       </c>
@@ -1903,14 +1578,8 @@
       <c r="D50" t="s">
         <v>9</v>
       </c>
-      <c r="E50" t="s">
-        <v>154</v>
-      </c>
-      <c r="F50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>67</v>
       </c>
@@ -1923,14 +1592,8 @@
       <c r="D51" t="s">
         <v>9</v>
       </c>
-      <c r="E51" t="s">
-        <v>154</v>
-      </c>
-      <c r="F51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>68</v>
       </c>
@@ -1943,14 +1606,8 @@
       <c r="D52" t="s">
         <v>9</v>
       </c>
-      <c r="E52" t="s">
-        <v>154</v>
-      </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>69</v>
       </c>
@@ -1963,14 +1620,8 @@
       <c r="D53" t="s">
         <v>9</v>
       </c>
-      <c r="E53" t="s">
-        <v>154</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>70</v>
       </c>
@@ -1983,14 +1634,8 @@
       <c r="D54" t="s">
         <v>9</v>
       </c>
-      <c r="E54" t="s">
-        <v>154</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>71</v>
       </c>
@@ -2003,14 +1648,8 @@
       <c r="D55" t="s">
         <v>9</v>
       </c>
-      <c r="E55" t="s">
-        <v>158</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>73</v>
       </c>
@@ -2023,14 +1662,8 @@
       <c r="D56" t="s">
         <v>9</v>
       </c>
-      <c r="E56" t="s">
-        <v>154</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -2043,14 +1676,8 @@
       <c r="D57" t="s">
         <v>9</v>
       </c>
-      <c r="E57" t="s">
-        <v>154</v>
-      </c>
-      <c r="F57">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -2063,14 +1690,8 @@
       <c r="D58" t="s">
         <v>9</v>
       </c>
-      <c r="E58" t="s">
-        <v>154</v>
-      </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>76</v>
       </c>
@@ -2083,14 +1704,8 @@
       <c r="D59" t="s">
         <v>9</v>
       </c>
-      <c r="E59" t="s">
-        <v>154</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>77</v>
       </c>
@@ -2103,14 +1718,8 @@
       <c r="D60" t="s">
         <v>9</v>
       </c>
-      <c r="E60" t="s">
-        <v>154</v>
-      </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>78</v>
       </c>
@@ -2123,14 +1732,8 @@
       <c r="D61" t="s">
         <v>9</v>
       </c>
-      <c r="E61" t="s">
-        <v>154</v>
-      </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>79</v>
       </c>
@@ -2143,14 +1746,8 @@
       <c r="D62" t="s">
         <v>9</v>
       </c>
-      <c r="E62" t="s">
-        <v>154</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -2163,14 +1760,8 @@
       <c r="D63" t="s">
         <v>9</v>
       </c>
-      <c r="E63" t="s">
-        <v>154</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>81</v>
       </c>
@@ -2183,14 +1774,8 @@
       <c r="D64" t="s">
         <v>9</v>
       </c>
-      <c r="E64" t="s">
-        <v>158</v>
-      </c>
-      <c r="F64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>82</v>
       </c>
@@ -2203,14 +1788,8 @@
       <c r="D65" t="s">
         <v>9</v>
       </c>
-      <c r="E65" t="s">
-        <v>154</v>
-      </c>
-      <c r="F65">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -2223,14 +1802,8 @@
       <c r="D66" t="s">
         <v>9</v>
       </c>
-      <c r="E66" t="s">
-        <v>154</v>
-      </c>
-      <c r="F66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>84</v>
       </c>
@@ -2243,14 +1816,8 @@
       <c r="D67" t="s">
         <v>9</v>
       </c>
-      <c r="E67" t="s">
-        <v>154</v>
-      </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>85</v>
       </c>
@@ -2263,14 +1830,8 @@
       <c r="D68" t="s">
         <v>9</v>
       </c>
-      <c r="E68" t="s">
-        <v>154</v>
-      </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -2283,14 +1844,8 @@
       <c r="D69" t="s">
         <v>9</v>
       </c>
-      <c r="E69" t="s">
-        <v>154</v>
-      </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>87</v>
       </c>
@@ -2303,14 +1858,8 @@
       <c r="D70" t="s">
         <v>9</v>
       </c>
-      <c r="E70" t="s">
-        <v>154</v>
-      </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>88</v>
       </c>
@@ -2323,14 +1872,8 @@
       <c r="D71" t="s">
         <v>9</v>
       </c>
-      <c r="E71" t="s">
-        <v>157</v>
-      </c>
-      <c r="F71">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>90</v>
       </c>
@@ -2343,14 +1886,8 @@
       <c r="D72" t="s">
         <v>9</v>
       </c>
-      <c r="E72" t="s">
-        <v>154</v>
-      </c>
-      <c r="F72">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>91</v>
       </c>
@@ -2363,14 +1900,8 @@
       <c r="D73" t="s">
         <v>9</v>
       </c>
-      <c r="E73" t="s">
-        <v>154</v>
-      </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>92</v>
       </c>
@@ -2383,14 +1914,8 @@
       <c r="D74" t="s">
         <v>9</v>
       </c>
-      <c r="E74" t="s">
-        <v>154</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>93</v>
       </c>
@@ -2403,14 +1928,8 @@
       <c r="D75" t="s">
         <v>9</v>
       </c>
-      <c r="E75" t="s">
-        <v>154</v>
-      </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>94</v>
       </c>
@@ -2423,14 +1942,8 @@
       <c r="D76" t="s">
         <v>9</v>
       </c>
-      <c r="E76" t="s">
-        <v>154</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>95</v>
       </c>
@@ -2443,14 +1956,8 @@
       <c r="D77" t="s">
         <v>9</v>
       </c>
-      <c r="E77" t="s">
-        <v>154</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>96</v>
       </c>
@@ -2463,14 +1970,8 @@
       <c r="D78" t="s">
         <v>9</v>
       </c>
-      <c r="E78" t="s">
-        <v>157</v>
-      </c>
-      <c r="F78">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>97</v>
       </c>
@@ -2483,14 +1984,8 @@
       <c r="D79" t="s">
         <v>9</v>
       </c>
-      <c r="E79" t="s">
-        <v>154</v>
-      </c>
-      <c r="F79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>98</v>
       </c>
@@ -2503,14 +1998,8 @@
       <c r="D80" t="s">
         <v>9</v>
       </c>
-      <c r="E80" t="s">
-        <v>154</v>
-      </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>99</v>
       </c>
@@ -2523,14 +2012,8 @@
       <c r="D81" t="s">
         <v>9</v>
       </c>
-      <c r="E81" t="s">
-        <v>154</v>
-      </c>
-      <c r="F81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>100</v>
       </c>
@@ -2543,14 +2026,8 @@
       <c r="D82" t="s">
         <v>9</v>
       </c>
-      <c r="E82" t="s">
-        <v>156</v>
-      </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>102</v>
       </c>
@@ -2563,14 +2040,8 @@
       <c r="D83" t="s">
         <v>9</v>
       </c>
-      <c r="E83" t="s">
-        <v>158</v>
-      </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>104</v>
       </c>
@@ -2583,14 +2054,8 @@
       <c r="D84" t="s">
         <v>9</v>
       </c>
-      <c r="E84" t="s">
-        <v>154</v>
-      </c>
-      <c r="F84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>106</v>
       </c>
@@ -2603,14 +2068,8 @@
       <c r="D85" t="s">
         <v>9</v>
       </c>
-      <c r="E85" t="s">
-        <v>157</v>
-      </c>
-      <c r="F85">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>107</v>
       </c>
@@ -2623,14 +2082,8 @@
       <c r="D86" t="s">
         <v>9</v>
       </c>
-      <c r="E86" t="s">
-        <v>154</v>
-      </c>
-      <c r="F86">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>108</v>
       </c>
@@ -2643,14 +2096,8 @@
       <c r="D87" t="s">
         <v>9</v>
       </c>
-      <c r="E87" t="s">
-        <v>154</v>
-      </c>
-      <c r="F87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>109</v>
       </c>
@@ -2663,14 +2110,8 @@
       <c r="D88" t="s">
         <v>9</v>
       </c>
-      <c r="E88" t="s">
-        <v>154</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>110</v>
       </c>
@@ -2683,14 +2124,8 @@
       <c r="D89" t="s">
         <v>9</v>
       </c>
-      <c r="E89" t="s">
-        <v>156</v>
-      </c>
-      <c r="F89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>111</v>
       </c>
@@ -2703,14 +2138,8 @@
       <c r="D90" t="s">
         <v>9</v>
       </c>
-      <c r="E90" t="s">
-        <v>154</v>
-      </c>
-      <c r="F90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>113</v>
       </c>
@@ -2723,14 +2152,8 @@
       <c r="D91" t="s">
         <v>9</v>
       </c>
-      <c r="E91" t="s">
-        <v>154</v>
-      </c>
-      <c r="F91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>114</v>
       </c>
@@ -2743,14 +2166,8 @@
       <c r="D92" t="s">
         <v>9</v>
       </c>
-      <c r="E92" t="s">
-        <v>157</v>
-      </c>
-      <c r="F92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>115</v>
       </c>
@@ -2763,14 +2180,8 @@
       <c r="D93" t="s">
         <v>9</v>
       </c>
-      <c r="E93" t="s">
-        <v>157</v>
-      </c>
-      <c r="F93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>118</v>
       </c>
@@ -2783,14 +2194,8 @@
       <c r="D94" t="s">
         <v>9</v>
       </c>
-      <c r="E94" t="s">
-        <v>154</v>
-      </c>
-      <c r="F94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>119</v>
       </c>
@@ -2803,14 +2208,8 @@
       <c r="D95" t="s">
         <v>9</v>
       </c>
-      <c r="E95" t="s">
-        <v>154</v>
-      </c>
-      <c r="F95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>120</v>
       </c>
@@ -2823,14 +2222,8 @@
       <c r="D96" t="s">
         <v>9</v>
       </c>
-      <c r="E96" t="s">
-        <v>156</v>
-      </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>121</v>
       </c>
@@ -2843,14 +2236,8 @@
       <c r="D97" t="s">
         <v>9</v>
       </c>
-      <c r="E97" t="s">
-        <v>154</v>
-      </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>122</v>
       </c>
@@ -2863,14 +2250,8 @@
       <c r="D98" t="s">
         <v>9</v>
       </c>
-      <c r="E98" t="s">
-        <v>154</v>
-      </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>124</v>
       </c>
@@ -2883,14 +2264,8 @@
       <c r="D99" t="s">
         <v>9</v>
       </c>
-      <c r="E99" t="s">
-        <v>157</v>
-      </c>
-      <c r="F99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>125</v>
       </c>
@@ -2903,14 +2278,8 @@
       <c r="D100" t="s">
         <v>9</v>
       </c>
-      <c r="E100" t="s">
-        <v>154</v>
-      </c>
-      <c r="F100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>137</v>
       </c>
@@ -2923,14 +2292,8 @@
       <c r="D101" t="s">
         <v>150</v>
       </c>
-      <c r="E101" t="s">
-        <v>159</v>
-      </c>
-      <c r="F101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>138</v>
       </c>
@@ -2943,14 +2306,8 @@
       <c r="D102" t="s">
         <v>150</v>
       </c>
-      <c r="E102" t="s">
-        <v>155</v>
-      </c>
-      <c r="F102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>139</v>
       </c>
@@ -2963,14 +2320,8 @@
       <c r="D103" t="s">
         <v>150</v>
       </c>
-      <c r="E103" t="s">
-        <v>160</v>
-      </c>
-      <c r="F103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>140</v>
       </c>
@@ -2983,14 +2334,8 @@
       <c r="D104" t="s">
         <v>150</v>
       </c>
-      <c r="E104" t="s">
-        <v>159</v>
-      </c>
-      <c r="F104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>141</v>
       </c>
@@ -3003,14 +2348,8 @@
       <c r="D105" t="s">
         <v>150</v>
       </c>
-      <c r="E105" t="s">
-        <v>155</v>
-      </c>
-      <c r="F105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>142</v>
       </c>
@@ -3023,14 +2362,8 @@
       <c r="D106" t="s">
         <v>150</v>
       </c>
-      <c r="E106" t="s">
-        <v>156</v>
-      </c>
-      <c r="F106">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>143</v>
       </c>
@@ -3043,14 +2376,8 @@
       <c r="D107" t="s">
         <v>150</v>
       </c>
-      <c r="E107" t="s">
-        <v>161</v>
-      </c>
-      <c r="F107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>144</v>
       </c>
@@ -3063,14 +2390,8 @@
       <c r="D108" t="s">
         <v>150</v>
       </c>
-      <c r="E108" t="s">
-        <v>159</v>
-      </c>
-      <c r="F108">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>145</v>
       </c>
@@ -3083,14 +2404,8 @@
       <c r="D109" t="s">
         <v>150</v>
       </c>
-      <c r="E109" t="s">
-        <v>155</v>
-      </c>
-      <c r="F109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>146</v>
       </c>
@@ -3103,14 +2418,8 @@
       <c r="D110" t="s">
         <v>150</v>
       </c>
-      <c r="E110" t="s">
-        <v>156</v>
-      </c>
-      <c r="F110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>147</v>
       </c>
@@ -3123,14 +2432,8 @@
       <c r="D111" t="s">
         <v>150</v>
       </c>
-      <c r="E111" t="s">
-        <v>161</v>
-      </c>
-      <c r="F111">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>148</v>
       </c>
@@ -3142,12 +2445,6 @@
       </c>
       <c r="D112" t="s">
         <v>150</v>
-      </c>
-      <c r="E112" t="s">
-        <v>157</v>
-      </c>
-      <c r="F112">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/db/tablas_procesadas/Materia.xlsx
+++ b/db/tablas_procesadas/Materia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Posgrado\Proyecto Titulacion\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F39AF44-B576-44E2-A9E5-9AAA5184F437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE93F05B-5DB5-476C-9969-6F9B1250B82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{73FF22F9-0A89-43F3-8B4B-2BA89E274F19}"/>
   </bookViews>
@@ -192,9 +192,6 @@
     <t>TC-INC-003</t>
   </si>
   <si>
-    <t>AMC-INC-003</t>
-  </si>
-  <si>
     <t>DI-INC-003</t>
   </si>
   <si>
@@ -499,6 +496,9 @@
   </si>
   <si>
     <t>tipo_materia</t>
+  </si>
+  <si>
+    <t>AM-INC-003</t>
   </si>
 </sst>
 </file>
@@ -881,7 +881,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1385,7 +1385,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
         <v>22</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
@@ -1427,7 +1427,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
         <v>28</v>
@@ -1441,7 +1441,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
         <v>48</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" t="s">
         <v>56</v>
-      </c>
-      <c r="B42" t="s">
-        <v>57</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" t="s">
         <v>16</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
         <v>28</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s">
         <v>48</v>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" t="s">
         <v>65</v>
-      </c>
-      <c r="B50" t="s">
-        <v>66</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B52" t="s">
         <v>28</v>
@@ -1609,7 +1609,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B53" t="s">
         <v>48</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" t="s">
         <v>71</v>
-      </c>
-      <c r="B55" t="s">
-        <v>72</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>3</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -1679,7 +1679,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B58" t="s">
         <v>28</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B59" t="s">
         <v>48</v>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B61" t="s">
         <v>16</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B62" t="s">
         <v>25</v>
@@ -1749,7 +1749,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B63" t="s">
         <v>2</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -1777,7 +1777,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B65" t="s">
         <v>37</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B66" t="s">
         <v>28</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B67" t="s">
         <v>48</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C68">
         <v>2</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B69" t="s">
         <v>25</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B70" t="s">
         <v>2</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71" t="s">
         <v>88</v>
-      </c>
-      <c r="B71" t="s">
-        <v>89</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -1889,7 +1889,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
         <v>28</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B74" t="s">
         <v>48</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B76" t="s">
         <v>25</v>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B77" t="s">
         <v>2</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B78" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B80" t="s">
         <v>28</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82" t="s">
         <v>100</v>
-      </c>
-      <c r="B82" t="s">
-        <v>101</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83" t="s">
         <v>102</v>
-      </c>
-      <c r="B83" t="s">
-        <v>103</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>103</v>
+      </c>
+      <c r="B84" t="s">
         <v>104</v>
-      </c>
-      <c r="B84" t="s">
-        <v>105</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C85">
         <v>3</v>
@@ -2071,10 +2071,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B86" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C86">
         <v>3</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B87" t="s">
         <v>28</v>
@@ -2099,10 +2099,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B89" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>110</v>
+      </c>
+      <c r="B90" t="s">
         <v>111</v>
-      </c>
-      <c r="B90" t="s">
-        <v>112</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B91" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C92">
         <v>3</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>114</v>
+      </c>
+      <c r="B93" t="s">
         <v>115</v>
-      </c>
-      <c r="B93" t="s">
-        <v>116</v>
       </c>
       <c r="C93">
         <v>3</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B94" t="s">
         <v>28</v>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -2211,10 +2211,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B96" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B97" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>121</v>
+      </c>
+      <c r="B98" t="s">
         <v>122</v>
-      </c>
-      <c r="B98" t="s">
-        <v>123</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C99">
         <v>3</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B100" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2281,170 +2281,170 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B101" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C101">
         <v>4</v>
       </c>
       <c r="D101" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B102" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C102">
         <v>4</v>
       </c>
       <c r="D102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C103">
         <v>4</v>
       </c>
       <c r="D103" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B104" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C104">
         <v>4</v>
       </c>
       <c r="D104" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B105" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C105">
         <v>4</v>
       </c>
       <c r="D105" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B106" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C106">
         <v>4</v>
       </c>
       <c r="D106" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B107" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B108" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C108">
         <v>4</v>
       </c>
       <c r="D108" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B109" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C109">
         <v>4</v>
       </c>
       <c r="D109" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B110" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C110">
         <v>4</v>
       </c>
       <c r="D110" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B111" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>147</v>
+      </c>
+      <c r="B112" t="s">
         <v>148</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112" t="s">
         <v>149</v>
-      </c>
-      <c r="C112">
-        <v>2</v>
-      </c>
-      <c r="D112" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/db/tablas_procesadas/Materia.xlsx
+++ b/db/tablas_procesadas/Materia.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Posgrado\Proyecto Titulacion\db\tablas_procesadas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE93F05B-5DB5-476C-9969-6F9B1250B82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2C0244-F8AE-465D-8681-350C9653B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{73FF22F9-0A89-43F3-8B4B-2BA89E274F19}"/>
+    <workbookView xWindow="8310" yWindow="3825" windowWidth="28785" windowHeight="15345" xr2:uid="{73FF22F9-0A89-43F3-8B4B-2BA89E274F19}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="163">
   <si>
     <t>nombre_materia</t>
   </si>
@@ -414,39 +414,6 @@
     <t>OF-IMC-003</t>
   </si>
   <si>
-    <t>Inc. Orq Cuerdas</t>
-  </si>
-  <si>
-    <t>Inc. Orq Guitarra</t>
-  </si>
-  <si>
-    <t>Inc. Orq Flautas</t>
-  </si>
-  <si>
-    <t>Orquesta de Cuerdas (A)</t>
-  </si>
-  <si>
-    <t>Orquesta de Guitarras (A)</t>
-  </si>
-  <si>
-    <t>Orquesta de Vientos (A)</t>
-  </si>
-  <si>
-    <t>Orquesta de Percusión (A)</t>
-  </si>
-  <si>
-    <t>Orquesta de Cuerdas (B)</t>
-  </si>
-  <si>
-    <t>Orquesta de Guitarras (B)</t>
-  </si>
-  <si>
-    <t>Orquesta de Vientos (B)</t>
-  </si>
-  <si>
-    <t>Orquestas de Precusion (B)</t>
-  </si>
-  <si>
     <t>INC-OC</t>
   </si>
   <si>
@@ -499,13 +466,73 @@
   </si>
   <si>
     <t>AM-INC-003</t>
+  </si>
+  <si>
+    <t>Inc. Orq Cuerdas (Seccional)</t>
+  </si>
+  <si>
+    <t>Inc. Orq Cuerdas (General)</t>
+  </si>
+  <si>
+    <t>Inc. Orq Guitarra (Seccional)</t>
+  </si>
+  <si>
+    <t>Inc. Orq Guitarra (General)</t>
+  </si>
+  <si>
+    <t>Inc. Orq Flautas (Seccional)</t>
+  </si>
+  <si>
+    <t>Inc. Orq Flautas (General)</t>
+  </si>
+  <si>
+    <t>Orquesta de Cuerdas (A) (Seccional)</t>
+  </si>
+  <si>
+    <t>Orquesta de Cuerdas (A) (General)</t>
+  </si>
+  <si>
+    <t>Orquesta de Guitarras (A) (Seccional)</t>
+  </si>
+  <si>
+    <t>Orquesta de Guitarras (A) (General)</t>
+  </si>
+  <si>
+    <t>Orquesta de Vientos (A) (Seccional)</t>
+  </si>
+  <si>
+    <t>Orquesta de Vientos (A) (General)</t>
+  </si>
+  <si>
+    <t>Orquesta de Cuerdas (B) (General)</t>
+  </si>
+  <si>
+    <t>Orquesta de Cuerdas (B) (Seccional)</t>
+  </si>
+  <si>
+    <t>Orquesta de Guitarras (B) (General)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orquesta de Percusión (A) </t>
+  </si>
+  <si>
+    <t>Orquesta de Guitarras (B) (Seccional)</t>
+  </si>
+  <si>
+    <t>Orquesta de Vientos (B) (Seccional)</t>
+  </si>
+  <si>
+    <t>Orquesta de Vientos (B) (General)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orquestas de Precusion (B) </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -870,18 +897,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA8CF66-513C-4C40-9688-A116B35459D8}">
-  <dimension ref="A1:D112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D121"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.21875" customWidth="1"/>
-    <col min="2" max="2" width="23.109375" customWidth="1"/>
-    <col min="3" max="3" width="21.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="3" max="3" width="21.875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -890,10 +917,10 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -907,7 +934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -921,7 +948,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -935,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -949,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -963,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -977,7 +1004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -991,7 +1018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1005,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1019,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1033,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1047,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1061,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1075,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1089,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1103,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1117,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -1131,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1145,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -1159,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -1173,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -1187,7 +1214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -1201,7 +1228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -1215,7 +1242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -1229,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -1243,7 +1270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -1257,7 +1284,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1271,7 +1298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -1285,7 +1312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -1299,7 +1326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -1313,7 +1340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -1327,7 +1354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -1341,7 +1368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -1355,7 +1382,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -1369,7 +1396,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1383,9 +1410,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
@@ -1397,7 +1424,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -1411,7 +1438,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -1425,7 +1452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -1439,7 +1466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -1453,7 +1480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>55</v>
       </c>
@@ -1467,7 +1494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>57</v>
       </c>
@@ -1481,7 +1508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -1495,7 +1522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -1509,7 +1536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -1523,7 +1550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -1537,7 +1564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>62</v>
       </c>
@@ -1551,7 +1578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -1565,7 +1592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -1579,7 +1606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -1593,7 +1620,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>67</v>
       </c>
@@ -1607,7 +1634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>68</v>
       </c>
@@ -1621,7 +1648,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>69</v>
       </c>
@@ -1635,7 +1662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>70</v>
       </c>
@@ -1649,7 +1676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>72</v>
       </c>
@@ -1663,7 +1690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>73</v>
       </c>
@@ -1677,7 +1704,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>74</v>
       </c>
@@ -1691,7 +1718,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>75</v>
       </c>
@@ -1705,7 +1732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>76</v>
       </c>
@@ -1719,7 +1746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>77</v>
       </c>
@@ -1733,7 +1760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>78</v>
       </c>
@@ -1747,7 +1774,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>79</v>
       </c>
@@ -1761,12 +1788,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>80</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -1775,7 +1802,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>81</v>
       </c>
@@ -1789,7 +1816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>82</v>
       </c>
@@ -1803,7 +1830,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -1817,7 +1844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>84</v>
       </c>
@@ -1831,7 +1858,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>85</v>
       </c>
@@ -1845,7 +1872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>86</v>
       </c>
@@ -1859,7 +1886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>87</v>
       </c>
@@ -1873,7 +1900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>89</v>
       </c>
@@ -1887,7 +1914,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -1901,7 +1928,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -1915,7 +1942,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -1929,7 +1956,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>93</v>
       </c>
@@ -1943,7 +1970,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -1957,7 +1984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>95</v>
       </c>
@@ -1971,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>96</v>
       </c>
@@ -1985,7 +2012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>97</v>
       </c>
@@ -1999,7 +2026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>98</v>
       </c>
@@ -2013,7 +2040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>99</v>
       </c>
@@ -2027,7 +2054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>101</v>
       </c>
@@ -2041,7 +2068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>103</v>
       </c>
@@ -2055,7 +2082,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>105</v>
       </c>
@@ -2063,13 +2090,13 @@
         <v>88</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
         <v>106</v>
       </c>
@@ -2083,7 +2110,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>107</v>
       </c>
@@ -2097,7 +2124,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>108</v>
       </c>
@@ -2111,7 +2138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>109</v>
       </c>
@@ -2125,7 +2152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
         <v>110</v>
       </c>
@@ -2139,7 +2166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>112</v>
       </c>
@@ -2153,7 +2180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>113</v>
       </c>
@@ -2161,13 +2188,13 @@
         <v>88</v>
       </c>
       <c r="C92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D92" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>114</v>
       </c>
@@ -2181,7 +2208,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>117</v>
       </c>
@@ -2195,7 +2222,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>118</v>
       </c>
@@ -2209,7 +2236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>119</v>
       </c>
@@ -2223,7 +2250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>120</v>
       </c>
@@ -2237,7 +2264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>121</v>
       </c>
@@ -2251,7 +2278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>123</v>
       </c>
@@ -2259,13 +2286,13 @@
         <v>88</v>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
         <v>124</v>
       </c>
@@ -2279,172 +2306,298 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
+        <v>125</v>
+      </c>
+      <c r="B101" t="s">
+        <v>143</v>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+      <c r="D101" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>125</v>
+      </c>
+      <c r="B102" t="s">
+        <v>144</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>126</v>
+      </c>
+      <c r="B103" t="s">
+        <v>145</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>126</v>
+      </c>
+      <c r="B104" t="s">
+        <v>146</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="D104" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>127</v>
+      </c>
+      <c r="B105" t="s">
+        <v>147</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>127</v>
+      </c>
+      <c r="B106" t="s">
+        <v>148</v>
+      </c>
+      <c r="C106">
+        <v>2</v>
+      </c>
+      <c r="D106" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>128</v>
+      </c>
+      <c r="B107" t="s">
+        <v>149</v>
+      </c>
+      <c r="C107">
+        <v>2</v>
+      </c>
+      <c r="D107" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>128</v>
+      </c>
+      <c r="B108" t="s">
+        <v>150</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>129</v>
+      </c>
+      <c r="B109" t="s">
+        <v>151</v>
+      </c>
+      <c r="C109">
+        <v>2</v>
+      </c>
+      <c r="D109" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>129</v>
+      </c>
+      <c r="B110" t="s">
+        <v>152</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
+      </c>
+      <c r="D110" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>130</v>
+      </c>
+      <c r="B111" t="s">
+        <v>153</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>130</v>
+      </c>
+      <c r="B112" t="s">
+        <v>154</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>131</v>
+      </c>
+      <c r="B113" t="s">
+        <v>158</v>
+      </c>
+      <c r="C113">
+        <v>2</v>
+      </c>
+      <c r="D113" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>132</v>
+      </c>
+      <c r="B114" t="s">
+        <v>156</v>
+      </c>
+      <c r="C114">
+        <v>2</v>
+      </c>
+      <c r="D114" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>132</v>
+      </c>
+      <c r="B115" t="s">
+        <v>155</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>133</v>
+      </c>
+      <c r="B116" t="s">
+        <v>159</v>
+      </c>
+      <c r="C116">
+        <v>2</v>
+      </c>
+      <c r="D116" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>133</v>
+      </c>
+      <c r="B117" t="s">
+        <v>157</v>
+      </c>
+      <c r="C117">
+        <v>2</v>
+      </c>
+      <c r="D117" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>134</v>
+      </c>
+      <c r="B118" t="s">
+        <v>160</v>
+      </c>
+      <c r="C118">
+        <v>2</v>
+      </c>
+      <c r="D118" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>134</v>
+      </c>
+      <c r="B119" t="s">
+        <v>161</v>
+      </c>
+      <c r="C119">
+        <v>2</v>
+      </c>
+      <c r="D119" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>135</v>
+      </c>
+      <c r="B120" t="s">
+        <v>162</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="D120" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
         <v>136</v>
       </c>
-      <c r="B101" t="s">
-        <v>125</v>
-      </c>
-      <c r="C101">
-        <v>4</v>
-      </c>
-      <c r="D101" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="B121" t="s">
         <v>137</v>
       </c>
-      <c r="B102" t="s">
-        <v>126</v>
-      </c>
-      <c r="C102">
-        <v>4</v>
-      </c>
-      <c r="D102" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
         <v>138</v>
-      </c>
-      <c r="B103" t="s">
-        <v>127</v>
-      </c>
-      <c r="C103">
-        <v>4</v>
-      </c>
-      <c r="D103" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>139</v>
-      </c>
-      <c r="B104" t="s">
-        <v>128</v>
-      </c>
-      <c r="C104">
-        <v>4</v>
-      </c>
-      <c r="D104" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>140</v>
-      </c>
-      <c r="B105" t="s">
-        <v>129</v>
-      </c>
-      <c r="C105">
-        <v>4</v>
-      </c>
-      <c r="D105" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>141</v>
-      </c>
-      <c r="B106" t="s">
-        <v>130</v>
-      </c>
-      <c r="C106">
-        <v>4</v>
-      </c>
-      <c r="D106" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>142</v>
-      </c>
-      <c r="B107" t="s">
-        <v>131</v>
-      </c>
-      <c r="C107">
-        <v>2</v>
-      </c>
-      <c r="D107" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>143</v>
-      </c>
-      <c r="B108" t="s">
-        <v>132</v>
-      </c>
-      <c r="C108">
-        <v>4</v>
-      </c>
-      <c r="D108" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>144</v>
-      </c>
-      <c r="B109" t="s">
-        <v>133</v>
-      </c>
-      <c r="C109">
-        <v>4</v>
-      </c>
-      <c r="D109" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>145</v>
-      </c>
-      <c r="B110" t="s">
-        <v>134</v>
-      </c>
-      <c r="C110">
-        <v>4</v>
-      </c>
-      <c r="D110" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>146</v>
-      </c>
-      <c r="B111" t="s">
-        <v>135</v>
-      </c>
-      <c r="C111">
-        <v>2</v>
-      </c>
-      <c r="D111" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>147</v>
-      </c>
-      <c r="B112" t="s">
-        <v>148</v>
-      </c>
-      <c r="C112">
-        <v>2</v>
-      </c>
-      <c r="D112" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/db/tablas_procesadas/Materia.xlsx
+++ b/db/tablas_procesadas/Materia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2212F64B-5EAC-4D8E-86BB-C498F82174CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468367A6-2BAB-4215-A4A5-EF35159E3121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{73FF22F9-0A89-43F3-8B4B-2BA89E274F19}"/>
+    <workbookView xWindow="7020" yWindow="2415" windowWidth="28785" windowHeight="15345" xr2:uid="{73FF22F9-0A89-43F3-8B4B-2BA89E274F19}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="138">
   <si>
     <t>nombre_materia</t>
   </si>
@@ -330,9 +330,6 @@
     <t>DM-IMC-003</t>
   </si>
   <si>
-    <t>AR-IMC-003</t>
-  </si>
-  <si>
     <t>ANM-IMC-002</t>
   </si>
   <si>
@@ -342,12 +339,6 @@
     <t>Orquesta Sinfonica</t>
   </si>
   <si>
-    <t>Orquestal</t>
-  </si>
-  <si>
-    <t>materia_id</t>
-  </si>
-  <si>
     <t>Practica Coral (J)</t>
   </si>
   <si>
@@ -393,15 +384,6 @@
     <t>Inc. Orquestal (Seccional)</t>
   </si>
   <si>
-    <t>INO</t>
-  </si>
-  <si>
-    <t>OA</t>
-  </si>
-  <si>
-    <t>OB</t>
-  </si>
-  <si>
     <t>Orquesta A (General)</t>
   </si>
   <si>
@@ -442,13 +424,40 @@
   </si>
   <si>
     <t>HA-IMC</t>
+  </si>
+  <si>
+    <t>Conjunto</t>
+  </si>
+  <si>
+    <t>id_materia</t>
+  </si>
+  <si>
+    <t>INOG</t>
+  </si>
+  <si>
+    <t>OAG</t>
+  </si>
+  <si>
+    <t>INOS</t>
+  </si>
+  <si>
+    <t>OAS</t>
+  </si>
+  <si>
+    <t>OBG</t>
+  </si>
+  <si>
+    <t>OBS</t>
+  </si>
+  <si>
+    <t>ARM-IMC-003</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,6 +469,12 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -485,9 +500,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -822,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA8CF66-513C-4C40-9688-A116B35459D8}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -835,7 +851,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -844,16 +860,16 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" t="s">
         <v>104</v>
-      </c>
-      <c r="E1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -870,10 +886,10 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -890,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -913,10 +929,10 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -933,10 +949,10 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -953,13 +969,13 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -976,10 +992,10 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -996,13 +1012,13 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1019,10 +1035,10 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1039,13 +1055,13 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1062,10 +1078,10 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1082,10 +1098,10 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1102,13 +1118,13 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1125,10 +1141,10 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1145,13 +1161,13 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1168,10 +1184,10 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1188,10 +1204,10 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1208,10 +1224,10 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1228,10 +1244,10 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1248,10 +1264,10 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1268,13 +1284,13 @@
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G21" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1291,13 +1307,13 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1314,15 +1330,15 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F23" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
@@ -1334,15 +1350,15 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
@@ -1354,10 +1370,10 @@
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F25" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1374,10 +1390,10 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1394,10 +1410,10 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1414,10 +1430,10 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1434,13 +1450,13 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1457,13 +1473,13 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1480,10 +1496,10 @@
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F31" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1500,10 +1516,10 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1520,10 +1536,10 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F33" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1540,10 +1556,10 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1560,18 +1576,18 @@
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F35" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G35" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
@@ -1583,13 +1599,13 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F36" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G36" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1606,10 +1622,10 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F37" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1626,10 +1642,10 @@
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F38" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1646,10 +1662,10 @@
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1666,10 +1682,10 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F40" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1686,18 +1702,18 @@
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F41" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G41" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s">
         <v>58</v>
@@ -1709,15 +1725,15 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F42" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
         <v>94</v>
@@ -1729,10 +1745,10 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1749,10 +1765,10 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F44" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1769,10 +1785,10 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F45" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1789,10 +1805,10 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F46" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1809,13 +1825,13 @@
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F47" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G47" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1832,10 +1848,10 @@
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F48" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1852,10 +1868,10 @@
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F49" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1872,10 +1888,10 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F50" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1892,10 +1908,10 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F51" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1912,10 +1928,10 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F52" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1932,10 +1948,10 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F53" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1952,10 +1968,10 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F54" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1972,13 +1988,13 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F55" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G55" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1995,10 +2011,10 @@
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F56" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2015,21 +2031,21 @@
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F57" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G57" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -2038,15 +2054,15 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F58" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B59" t="s">
         <v>35</v>
@@ -2058,10 +2074,10 @@
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F59" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2078,10 +2094,10 @@
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F60" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2098,10 +2114,10 @@
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F61" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2118,10 +2134,10 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F62" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2138,10 +2154,10 @@
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F63" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2158,18 +2174,18 @@
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F64" t="s">
+        <v>107</v>
+      </c>
+      <c r="G64" t="s">
         <v>110</v>
-      </c>
-      <c r="G64" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
@@ -2181,10 +2197,10 @@
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F65" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2201,10 +2217,10 @@
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F66" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2221,10 +2237,10 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F67" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2241,10 +2257,10 @@
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F68" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2261,10 +2277,10 @@
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F69" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2281,13 +2297,13 @@
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F70" t="s">
+        <v>107</v>
+      </c>
+      <c r="G70" t="s">
         <v>110</v>
-      </c>
-      <c r="G70" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2304,10 +2320,10 @@
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F71" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2324,10 +2340,10 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F72" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2344,10 +2360,10 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F73" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2364,10 +2380,10 @@
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F74" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2375,7 +2391,7 @@
         <v>87</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -2384,15 +2400,15 @@
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F75" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B76" t="s">
         <v>93</v>
@@ -2404,10 +2420,10 @@
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F76" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2424,10 +2440,10 @@
         <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F77" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2444,10 +2460,10 @@
         <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F78" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2464,10 +2480,10 @@
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F79" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2484,18 +2500,18 @@
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F80" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B81" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -2504,10 +2520,10 @@
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F81" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2524,10 +2540,10 @@
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F82" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2544,15 +2560,15 @@
         <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F83" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="B84" t="s">
         <v>84</v>
@@ -2564,15 +2580,15 @@
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F84" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B85" t="s">
         <v>92</v>
@@ -2584,156 +2600,160 @@
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F85" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B86" t="s">
-        <v>116</v>
-      </c>
-      <c r="C86">
+        <v>113</v>
+      </c>
+      <c r="C86" s="1">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E86" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F86" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B87" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E87" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F87" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B88" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E88" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F88" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B89" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E89" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F89" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="13.5" customHeight="1">
       <c r="A90" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="B90" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E90" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F90" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B91" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E91" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F91" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" t="s">
         <v>99</v>
       </c>
-      <c r="B92" t="s">
-        <v>100</v>
-      </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E92" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F92" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G92" t="s">
-        <v>115</v>
-      </c>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
